--- a/docs/詳細設計書/設計書_在庫一覧画面.xlsx
+++ b/docs/詳細設計書/設計書_在庫一覧画面.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="14055"/>
+    <workbookView windowWidth="19815" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="12" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="137">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -209,6 +209,9 @@
     <t>想定外エラー：プルダウンに想定しないvalue</t>
   </si>
   <si>
+    <t>クリック時：分類名をすべてを表示</t>
+  </si>
+  <si>
     <t>　名称</t>
   </si>
   <si>
@@ -219,6 +222,9 @@
   </si>
   <si>
     <t>文字数制限：20文字</t>
+  </si>
+  <si>
+    <t>入力時: 制限を超えたら警告を表示</t>
   </si>
   <si>
     <t>　個数</t>
@@ -231,12 +237,18 @@
 文字数制限：0未満10000以上の入力</t>
   </si>
   <si>
+    <t>入力時: 適切な文字数、型でない場合警告を表示</t>
+  </si>
+  <si>
     <t>　数量条件</t>
   </si>
   <si>
     <t>「以上」または「以下」のプルダウン選択が可能</t>
   </si>
   <si>
+    <t>クリック時：「以上」または「以下」を表示</t>
+  </si>
+  <si>
     <t>　検索</t>
   </si>
   <si>
@@ -244,6 +256,9 @@
   </si>
   <si>
     <t>在庫情報検索を行うフォームを送信するボタン</t>
+  </si>
+  <si>
+    <t>クリック時: 検索結果を表示</t>
   </si>
   <si>
     <t>在庫一覧 テーブル</t>
@@ -431,12 +446,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="33">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -502,24 +517,6 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
       <charset val="128"/>
@@ -537,16 +534,12 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -557,62 +550,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -632,13 +570,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -647,18 +578,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -670,15 +622,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -693,14 +647,45 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,7 +730,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -757,109 +760,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,13 +784,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,48 +880,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1130,46 +1091,49 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </left>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="dotted">
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="dotted">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="dotted">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1200,11 +1164,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1218,6 +1188,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1226,160 +1220,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1665,30 +1674,15 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1707,70 +1701,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
@@ -1788,14 +1767,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1812,49 +1788,55 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -2895,513 +2877,513 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="151"/>
-      <c r="B2" s="153" t="s">
+      <c r="A2" s="143"/>
+      <c r="B2" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="154" t="s">
+      <c r="C2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="154" t="s">
+      <c r="D2" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="154" t="s">
+      <c r="E2" s="68" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="151"/>
-      <c r="B3" s="155" t="s">
+      <c r="A3" s="143"/>
+      <c r="B3" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="156">
+      <c r="C3" s="147">
         <v>45636</v>
       </c>
-      <c r="D3" s="157" t="s">
+      <c r="D3" s="148" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="157" t="s">
+      <c r="E3" s="148" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="33" spans="1:5">
-      <c r="A4" s="151"/>
-      <c r="B4" s="155" t="s">
+      <c r="A4" s="143"/>
+      <c r="B4" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="156">
+      <c r="C4" s="147">
         <v>45729</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="148" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="149" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="151"/>
-      <c r="B5" s="155"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
+      <c r="A5" s="143"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="148"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="151"/>
-      <c r="B6" s="155"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
+      <c r="A6" s="143"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="151"/>
-      <c r="B7" s="155"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="151"/>
-      <c r="B8" s="155"/>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
+      <c r="A8" s="143"/>
+      <c r="B8" s="146"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="151"/>
-      <c r="B9" s="155"/>
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
+      <c r="A9" s="143"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="148"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="151"/>
-      <c r="B10" s="155"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
+      <c r="A10" s="143"/>
+      <c r="B10" s="146"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="151"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="148"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="151"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
+      <c r="A12" s="143"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="148"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="151"/>
-      <c r="B13" s="155"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="157"/>
+      <c r="A13" s="143"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="148"/>
+      <c r="D13" s="148"/>
+      <c r="E13" s="148"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="151"/>
-      <c r="B14" s="155"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
+      <c r="A14" s="143"/>
+      <c r="B14" s="146"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="151"/>
-      <c r="B15" s="155"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
+      <c r="A15" s="143"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="151"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
+      <c r="A16" s="143"/>
+      <c r="B16" s="146"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="148"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="151"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="148"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="151"/>
-      <c r="B18" s="155"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="148"/>
+      <c r="D18" s="148"/>
+      <c r="E18" s="148"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="151"/>
-      <c r="B19" s="155"/>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="148"/>
+      <c r="D19" s="148"/>
+      <c r="E19" s="148"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="151"/>
-      <c r="B20" s="155"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="148"/>
+      <c r="D20" s="148"/>
+      <c r="E20" s="148"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="151"/>
-      <c r="B21" s="155"/>
-      <c r="C21" s="157"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="148"/>
+      <c r="D21" s="148"/>
+      <c r="E21" s="148"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="151"/>
-      <c r="B22" s="155"/>
-      <c r="C22" s="157"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="146"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="151"/>
-      <c r="B23" s="155"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="151"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="157"/>
-      <c r="D24" s="157"/>
-      <c r="E24" s="157"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="148"/>
+      <c r="D24" s="148"/>
+      <c r="E24" s="148"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="151"/>
-      <c r="B25" s="155"/>
-      <c r="C25" s="157"/>
-      <c r="D25" s="157"/>
-      <c r="E25" s="157"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="151"/>
-      <c r="B26" s="155"/>
-      <c r="C26" s="157"/>
-      <c r="D26" s="157"/>
-      <c r="E26" s="157"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="151"/>
-      <c r="B27" s="155"/>
-      <c r="C27" s="157"/>
-      <c r="D27" s="157"/>
-      <c r="E27" s="157"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="146"/>
+      <c r="C27" s="148"/>
+      <c r="D27" s="148"/>
+      <c r="E27" s="148"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="151"/>
-      <c r="B28" s="155"/>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
-      <c r="E28" s="157"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="148"/>
+      <c r="D28" s="148"/>
+      <c r="E28" s="148"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="151"/>
-      <c r="B29" s="155"/>
-      <c r="C29" s="157"/>
-      <c r="D29" s="157"/>
-      <c r="E29" s="157"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="146"/>
+      <c r="C29" s="148"/>
+      <c r="D29" s="148"/>
+      <c r="E29" s="148"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="151"/>
-      <c r="B30" s="155"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="157"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="146"/>
+      <c r="C30" s="148"/>
+      <c r="D30" s="148"/>
+      <c r="E30" s="148"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="151"/>
-      <c r="B31" s="155"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
+      <c r="A31" s="143"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="151"/>
-      <c r="B32" s="155"/>
-      <c r="C32" s="157"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
+      <c r="A32" s="143"/>
+      <c r="B32" s="146"/>
+      <c r="C32" s="148"/>
+      <c r="D32" s="148"/>
+      <c r="E32" s="148"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="151"/>
-      <c r="B33" s="155"/>
-      <c r="C33" s="157"/>
-      <c r="D33" s="157"/>
-      <c r="E33" s="157"/>
+      <c r="A33" s="143"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="151"/>
-      <c r="B34" s="155"/>
-      <c r="C34" s="157"/>
-      <c r="D34" s="157"/>
-      <c r="E34" s="157"/>
+      <c r="A34" s="143"/>
+      <c r="B34" s="146"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="148"/>
+      <c r="E34" s="148"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="151"/>
-      <c r="B35" s="155"/>
-      <c r="C35" s="157"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="157"/>
+      <c r="A35" s="143"/>
+      <c r="B35" s="146"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="151"/>
-      <c r="B36" s="155"/>
-      <c r="C36" s="157"/>
-      <c r="D36" s="157"/>
-      <c r="E36" s="157"/>
+      <c r="A36" s="143"/>
+      <c r="B36" s="146"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="148"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="151"/>
-      <c r="B37" s="155"/>
-      <c r="C37" s="157"/>
-      <c r="D37" s="157"/>
-      <c r="E37" s="157"/>
+      <c r="A37" s="143"/>
+      <c r="B37" s="146"/>
+      <c r="C37" s="148"/>
+      <c r="D37" s="148"/>
+      <c r="E37" s="148"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="151"/>
-      <c r="B38" s="155"/>
-      <c r="C38" s="157"/>
-      <c r="D38" s="157"/>
-      <c r="E38" s="157"/>
+      <c r="A38" s="143"/>
+      <c r="B38" s="146"/>
+      <c r="C38" s="148"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="151"/>
-      <c r="B39" s="155"/>
-      <c r="C39" s="157"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
+      <c r="A39" s="143"/>
+      <c r="B39" s="146"/>
+      <c r="C39" s="148"/>
+      <c r="D39" s="148"/>
+      <c r="E39" s="148"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="151"/>
-      <c r="B40" s="155"/>
-      <c r="C40" s="157"/>
-      <c r="D40" s="157"/>
-      <c r="E40" s="157"/>
+      <c r="A40" s="143"/>
+      <c r="B40" s="146"/>
+      <c r="C40" s="148"/>
+      <c r="D40" s="148"/>
+      <c r="E40" s="148"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="151"/>
-      <c r="B41" s="155"/>
-      <c r="C41" s="157"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="157"/>
+      <c r="A41" s="143"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="148"/>
+      <c r="D41" s="148"/>
+      <c r="E41" s="148"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="151"/>
-      <c r="B42" s="155"/>
-      <c r="C42" s="157"/>
-      <c r="D42" s="157"/>
-      <c r="E42" s="157"/>
+      <c r="A42" s="143"/>
+      <c r="B42" s="146"/>
+      <c r="C42" s="148"/>
+      <c r="D42" s="148"/>
+      <c r="E42" s="148"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="151"/>
-      <c r="B43" s="155"/>
-      <c r="C43" s="157"/>
-      <c r="D43" s="157"/>
-      <c r="E43" s="157"/>
+      <c r="A43" s="143"/>
+      <c r="B43" s="146"/>
+      <c r="C43" s="148"/>
+      <c r="D43" s="148"/>
+      <c r="E43" s="148"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="151"/>
-      <c r="B44" s="155"/>
-      <c r="C44" s="157"/>
-      <c r="D44" s="157"/>
-      <c r="E44" s="157"/>
+      <c r="A44" s="143"/>
+      <c r="B44" s="146"/>
+      <c r="C44" s="148"/>
+      <c r="D44" s="148"/>
+      <c r="E44" s="148"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="151"/>
-      <c r="B45" s="155"/>
-      <c r="C45" s="157"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="157"/>
+      <c r="A45" s="143"/>
+      <c r="B45" s="146"/>
+      <c r="C45" s="148"/>
+      <c r="D45" s="148"/>
+      <c r="E45" s="148"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="151"/>
-      <c r="B46" s="155"/>
-      <c r="C46" s="157"/>
-      <c r="D46" s="157"/>
-      <c r="E46" s="157"/>
+      <c r="A46" s="143"/>
+      <c r="B46" s="146"/>
+      <c r="C46" s="148"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="148"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="151"/>
-      <c r="B47" s="155"/>
-      <c r="C47" s="157"/>
-      <c r="D47" s="157"/>
-      <c r="E47" s="157"/>
+      <c r="A47" s="143"/>
+      <c r="B47" s="146"/>
+      <c r="C47" s="148"/>
+      <c r="D47" s="148"/>
+      <c r="E47" s="148"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="151"/>
-      <c r="B48" s="155"/>
-      <c r="C48" s="157"/>
-      <c r="D48" s="157"/>
-      <c r="E48" s="157"/>
+      <c r="A48" s="143"/>
+      <c r="B48" s="146"/>
+      <c r="C48" s="148"/>
+      <c r="D48" s="148"/>
+      <c r="E48" s="148"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="151"/>
-      <c r="B49" s="155"/>
-      <c r="C49" s="157"/>
-      <c r="D49" s="157"/>
-      <c r="E49" s="157"/>
+      <c r="A49" s="143"/>
+      <c r="B49" s="146"/>
+      <c r="C49" s="148"/>
+      <c r="D49" s="148"/>
+      <c r="E49" s="148"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="151"/>
-      <c r="B50" s="155"/>
-      <c r="C50" s="157"/>
-      <c r="D50" s="157"/>
-      <c r="E50" s="157"/>
+      <c r="A50" s="143"/>
+      <c r="B50" s="146"/>
+      <c r="C50" s="148"/>
+      <c r="D50" s="148"/>
+      <c r="E50" s="148"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="151"/>
-      <c r="B51" s="155"/>
-      <c r="C51" s="157"/>
-      <c r="D51" s="157"/>
-      <c r="E51" s="157"/>
+      <c r="A51" s="143"/>
+      <c r="B51" s="146"/>
+      <c r="C51" s="148"/>
+      <c r="D51" s="148"/>
+      <c r="E51" s="148"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="151"/>
-      <c r="B52" s="155"/>
-      <c r="C52" s="157"/>
-      <c r="D52" s="157"/>
-      <c r="E52" s="157"/>
+      <c r="A52" s="143"/>
+      <c r="B52" s="146"/>
+      <c r="C52" s="148"/>
+      <c r="D52" s="148"/>
+      <c r="E52" s="148"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="151"/>
-      <c r="B53" s="155"/>
-      <c r="C53" s="157"/>
-      <c r="D53" s="157"/>
-      <c r="E53" s="157"/>
+      <c r="A53" s="143"/>
+      <c r="B53" s="146"/>
+      <c r="C53" s="148"/>
+      <c r="D53" s="148"/>
+      <c r="E53" s="148"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="151"/>
-      <c r="B54" s="155"/>
-      <c r="C54" s="157"/>
-      <c r="D54" s="157"/>
-      <c r="E54" s="157"/>
+      <c r="A54" s="143"/>
+      <c r="B54" s="146"/>
+      <c r="C54" s="148"/>
+      <c r="D54" s="148"/>
+      <c r="E54" s="148"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="151"/>
-      <c r="B55" s="155"/>
-      <c r="C55" s="157"/>
-      <c r="D55" s="157"/>
-      <c r="E55" s="157"/>
+      <c r="A55" s="143"/>
+      <c r="B55" s="146"/>
+      <c r="C55" s="148"/>
+      <c r="D55" s="148"/>
+      <c r="E55" s="148"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="151"/>
-      <c r="B56" s="155"/>
-      <c r="C56" s="157"/>
-      <c r="D56" s="157"/>
-      <c r="E56" s="157"/>
+      <c r="A56" s="143"/>
+      <c r="B56" s="146"/>
+      <c r="C56" s="148"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="148"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="151"/>
-      <c r="B57" s="155"/>
-      <c r="C57" s="157"/>
-      <c r="D57" s="157"/>
-      <c r="E57" s="157"/>
+      <c r="A57" s="143"/>
+      <c r="B57" s="146"/>
+      <c r="C57" s="148"/>
+      <c r="D57" s="148"/>
+      <c r="E57" s="148"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="151"/>
-      <c r="B58" s="155"/>
-      <c r="C58" s="157"/>
-      <c r="D58" s="157"/>
-      <c r="E58" s="157"/>
+      <c r="A58" s="143"/>
+      <c r="B58" s="146"/>
+      <c r="C58" s="148"/>
+      <c r="D58" s="148"/>
+      <c r="E58" s="148"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="151"/>
-      <c r="B59" s="155"/>
-      <c r="C59" s="157"/>
-      <c r="D59" s="157"/>
-      <c r="E59" s="157"/>
+      <c r="A59" s="143"/>
+      <c r="B59" s="146"/>
+      <c r="C59" s="148"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="151"/>
-      <c r="B60" s="155"/>
-      <c r="C60" s="157"/>
-      <c r="D60" s="157"/>
-      <c r="E60" s="157"/>
+      <c r="A60" s="143"/>
+      <c r="B60" s="146"/>
+      <c r="C60" s="148"/>
+      <c r="D60" s="148"/>
+      <c r="E60" s="148"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="151"/>
-      <c r="B61" s="155"/>
-      <c r="C61" s="157"/>
-      <c r="D61" s="157"/>
-      <c r="E61" s="157"/>
+      <c r="A61" s="143"/>
+      <c r="B61" s="146"/>
+      <c r="C61" s="148"/>
+      <c r="D61" s="148"/>
+      <c r="E61" s="148"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="151"/>
-      <c r="B62" s="155"/>
-      <c r="C62" s="157"/>
-      <c r="D62" s="157"/>
-      <c r="E62" s="157"/>
+      <c r="A62" s="143"/>
+      <c r="B62" s="146"/>
+      <c r="C62" s="148"/>
+      <c r="D62" s="148"/>
+      <c r="E62" s="148"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="151"/>
-      <c r="B63" s="155"/>
-      <c r="C63" s="157"/>
-      <c r="D63" s="157"/>
-      <c r="E63" s="157"/>
+      <c r="A63" s="143"/>
+      <c r="B63" s="146"/>
+      <c r="C63" s="148"/>
+      <c r="D63" s="148"/>
+      <c r="E63" s="148"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="151"/>
-      <c r="B64" s="155"/>
-      <c r="C64" s="157"/>
-      <c r="D64" s="157"/>
-      <c r="E64" s="157"/>
+      <c r="A64" s="143"/>
+      <c r="B64" s="146"/>
+      <c r="C64" s="148"/>
+      <c r="D64" s="148"/>
+      <c r="E64" s="148"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="151"/>
-      <c r="B65" s="155"/>
-      <c r="C65" s="157"/>
-      <c r="D65" s="157"/>
-      <c r="E65" s="157"/>
+      <c r="A65" s="143"/>
+      <c r="B65" s="146"/>
+      <c r="C65" s="148"/>
+      <c r="D65" s="148"/>
+      <c r="E65" s="148"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="151"/>
-      <c r="B66" s="155"/>
-      <c r="C66" s="157"/>
-      <c r="D66" s="157"/>
-      <c r="E66" s="157"/>
+      <c r="A66" s="143"/>
+      <c r="B66" s="146"/>
+      <c r="C66" s="148"/>
+      <c r="D66" s="148"/>
+      <c r="E66" s="148"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="151"/>
-      <c r="B67" s="155"/>
-      <c r="C67" s="157"/>
-      <c r="D67" s="157"/>
-      <c r="E67" s="157"/>
+      <c r="A67" s="143"/>
+      <c r="B67" s="146"/>
+      <c r="C67" s="148"/>
+      <c r="D67" s="148"/>
+      <c r="E67" s="148"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="151"/>
-      <c r="B68" s="155"/>
-      <c r="C68" s="157"/>
-      <c r="D68" s="157"/>
-      <c r="E68" s="157"/>
+      <c r="A68" s="143"/>
+      <c r="B68" s="146"/>
+      <c r="C68" s="148"/>
+      <c r="D68" s="148"/>
+      <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="151"/>
-      <c r="B69" s="152"/>
-      <c r="C69" s="151"/>
-      <c r="D69" s="151"/>
-      <c r="E69" s="151"/>
+      <c r="A69" s="143"/>
+      <c r="B69" s="144"/>
+      <c r="C69" s="143"/>
+      <c r="D69" s="143"/>
+      <c r="E69" s="143"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4697,8 +4679,8 @@
     <col min="7" max="7" width="67.837037037037" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.2962962962963" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.1259259259259" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.4444444444444" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5555555555556" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7925925925926" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5333333333333" style="1" customWidth="1"/>
     <col min="12" max="14" width="13.4444444444444" style="1" customWidth="1"/>
     <col min="15" max="15" width="3.71111111111111" style="1"/>
     <col min="16" max="17" width="13.4444444444444" style="1" customWidth="1"/>
@@ -4708,34 +4690,34 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
       <c r="F1" s="68" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="97" t="s">
+      <c r="H1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="138" t="s">
+      <c r="I1" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="97" t="s">
+      <c r="J1" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="139">
+      <c r="K1" s="128">
         <v>45566</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="98"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -4746,13 +4728,13 @@
       <c r="G2" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="99"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="141"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="130"/>
     </row>
     <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="98"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -4763,479 +4745,479 @@
       <c r="G3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="97" t="s">
+      <c r="H3" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="138"/>
-      <c r="J3" s="97" t="s">
+      <c r="I3" s="98"/>
+      <c r="J3" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="139"/>
+      <c r="K3" s="128"/>
     </row>
     <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="103" t="s">
+      <c r="G4" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="104"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="143"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="132"/>
     </row>
     <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="105"/>
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="145"/>
+      <c r="A5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="133"/>
     </row>
     <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113" t="s">
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="114" t="s">
+      <c r="F6" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="115" t="s">
+      <c r="G6" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="146"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="134"/>
     </row>
     <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118" t="s">
+      <c r="A7" s="110"/>
+      <c r="B7" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="121" t="s">
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="122" t="s">
+      <c r="G7" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="123" t="s">
+      <c r="H7" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148" t="s">
+      <c r="I7" s="135"/>
+      <c r="J7" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="149"/>
+      <c r="K7" s="137"/>
     </row>
     <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="124">
+      <c r="A8" s="115">
         <v>1</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="116" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="126" t="s">
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="126" t="s">
+      <c r="G8" s="116" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="127" t="s">
+      <c r="H8" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="127"/>
-      <c r="J8" s="127" t="s">
+      <c r="I8" s="117"/>
+      <c r="J8" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="127"/>
+      <c r="K8" s="117"/>
     </row>
     <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="124">
-        <f t="shared" ref="A9:A19" si="0">A8+1</f>
+      <c r="A9" s="115">
+        <f t="shared" ref="A9:A21" si="0">A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126" t="s">
+      <c r="C9" s="116"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="126" t="s">
+      <c r="G9" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="127" t="s">
+      <c r="H9" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="127"/>
-      <c r="J9" s="127" t="s">
+      <c r="I9" s="117"/>
+      <c r="J9" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="127"/>
+      <c r="K9" s="117"/>
     </row>
     <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="124">
+      <c r="A10" s="115">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B10" s="125" t="s">
+      <c r="B10" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="126" t="s">
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="126" t="s">
+      <c r="G10" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="128" t="s">
+      <c r="H10" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="128"/>
-      <c r="J10" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="127"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="117"/>
     </row>
     <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="124">
+      <c r="A11" s="115">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B11" s="125" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="126" t="s">
+      <c r="B11" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="126" t="s">
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="127" t="s">
+      <c r="G11" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="127"/>
+      <c r="H11" s="117" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="117"/>
+      <c r="J11" s="138" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="139"/>
     </row>
     <row r="12" ht="45" customHeight="1" spans="1:11">
-      <c r="A12" s="124">
+      <c r="A12" s="115">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B12" s="125" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="126" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="126" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="129" t="s">
+      <c r="B12" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="128"/>
-      <c r="J12" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="127"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="116" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="118"/>
+      <c r="J12" s="138" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="139"/>
     </row>
     <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="124">
+      <c r="A13" s="115">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B13" s="125" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="126" t="s">
+      <c r="B13" s="116" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="126" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="128" t="s">
+      <c r="G13" s="116" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="128"/>
-      <c r="J13" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="127"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" s="117"/>
     </row>
     <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="124">
+      <c r="A14" s="115">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B14" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="126" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="126" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="127" t="s">
+      <c r="B14" s="116" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="116" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="127"/>
-      <c r="J14" s="127" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="127"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="140" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="141"/>
     </row>
     <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="124">
+      <c r="A15" s="115">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B15" s="125" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="125"/>
-      <c r="F15" s="126" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="126" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="127" t="s">
+      <c r="B15" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="116" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127" t="s">
+      <c r="I15" s="117"/>
+      <c r="J15" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="127"/>
+      <c r="K15" s="117"/>
     </row>
     <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="124">
+      <c r="A16" s="115">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B16" s="125" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="126" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="126" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="127" t="s">
+      <c r="B16" s="116" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="116" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127" t="s">
+      <c r="I16" s="117"/>
+      <c r="J16" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="127"/>
+      <c r="K16" s="117"/>
     </row>
     <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="124">
+      <c r="A17" s="115">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B17" s="125" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="126" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="126" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="127" t="s">
+      <c r="B17" s="116" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="116" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127" t="s">
+      <c r="I17" s="117"/>
+      <c r="J17" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="127"/>
+      <c r="K17" s="117"/>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="124">
-        <f>A17+1</f>
+      <c r="A18" s="115">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="125" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="126" t="s">
+      <c r="B18" s="116" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="126" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="127" t="s">
+      <c r="G18" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="127"/>
-      <c r="J18" s="127" t="s">
+      <c r="I18" s="117"/>
+      <c r="J18" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="127"/>
+      <c r="K18" s="117"/>
     </row>
     <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="124">
-        <f>A18+1</f>
+      <c r="A19" s="115">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B19" s="125" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126" t="s">
+      <c r="B19" s="116" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="126" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="127" t="s">
+      <c r="G19" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="127"/>
-      <c r="J19" s="127" t="s">
+      <c r="I19" s="117"/>
+      <c r="J19" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="127"/>
+      <c r="K19" s="117"/>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="124">
-        <f>A19+1</f>
+      <c r="A20" s="115">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="125" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="126" t="s">
+      <c r="B20" s="116" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="130" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="127" t="s">
+      <c r="G20" s="120" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="127"/>
-      <c r="J20" s="127" t="s">
+      <c r="I20" s="117"/>
+      <c r="J20" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="127"/>
+      <c r="K20" s="117"/>
     </row>
     <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="124">
-        <f>A20+1</f>
+      <c r="A21" s="115">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B21" s="125" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="125"/>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="126" t="s">
+      <c r="B21" s="116" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="130" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="127" t="s">
+      <c r="G21" s="120" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127" t="s">
+      <c r="I21" s="117"/>
+      <c r="J21" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="127"/>
+      <c r="K21" s="117"/>
     </row>
     <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="131"/>
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
+      <c r="A22" s="121"/>
+      <c r="B22" s="116"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
     </row>
     <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="132"/>
-      <c r="B23" s="133"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="135"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="137"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="150"/>
+      <c r="A23" s="122"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="63">
@@ -5325,7 +5307,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:37">
       <c r="A1" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5516,7 +5498,7 @@
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="55" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="56"/>
@@ -5558,7 +5540,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:37">
       <c r="A6" s="89" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B6" s="90"/>
       <c r="C6" s="90"/>
@@ -5599,7 +5581,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:37">
       <c r="A7" s="91" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B7" s="91"/>
       <c r="C7" s="91"/>
@@ -5641,7 +5623,7 @@
     <row r="8" customHeight="1" spans="1:37">
       <c r="A8" s="64"/>
       <c r="B8" s="71" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
@@ -5764,7 +5746,7 @@
       <c r="C12" s="13"/>
       <c r="G12" s="27"/>
       <c r="H12" s="15" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AJ12" s="27"/>
     </row>
@@ -5776,28 +5758,28 @@
         <v>55</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="N13" s="33" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O13" s="35"/>
       <c r="P13" s="35"/>
       <c r="Q13" s="39"/>
       <c r="S13" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="T13" s="33"/>
       <c r="U13" s="35"/>
       <c r="V13" s="35"/>
       <c r="W13" s="39"/>
       <c r="Y13" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="Z13" s="33"/>
       <c r="AA13" s="39"/>
       <c r="AB13" s="23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AC13" s="23"/>
       <c r="AJ13" s="27"/>
@@ -5813,30 +5795,30 @@
       <c r="C15" s="13"/>
       <c r="G15" s="27"/>
       <c r="J15" s="45" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K15" s="45"/>
       <c r="L15" s="45"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O15" s="45"/>
       <c r="P15" s="45"/>
       <c r="Q15" s="45"/>
       <c r="R15" s="45" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S15" s="45"/>
       <c r="T15" s="93" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="U15" s="93"/>
       <c r="V15" s="93"/>
       <c r="W15" s="93"/>
       <c r="X15" s="93"/>
       <c r="Y15" s="46" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Z15" s="51"/>
       <c r="AA15" s="51"/>
@@ -5853,13 +5835,13 @@
       <c r="C16" s="13"/>
       <c r="G16" s="27"/>
       <c r="J16" s="23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
       <c r="N16" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
@@ -5869,14 +5851,14 @@
       </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="U16" s="23"/>
       <c r="V16" s="23"/>
       <c r="W16" s="23"/>
       <c r="X16" s="23"/>
       <c r="Y16" s="33" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
@@ -5893,30 +5875,30 @@
       <c r="C17" s="13"/>
       <c r="G17" s="27"/>
       <c r="J17" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
       <c r="M17" s="23"/>
       <c r="N17" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
       <c r="R17" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S17" s="23"/>
       <c r="T17" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U17" s="35"/>
       <c r="V17" s="35"/>
       <c r="W17" s="35"/>
       <c r="X17" s="39"/>
       <c r="Y17" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z17" s="35"/>
       <c r="AA17" s="35"/>
@@ -5933,30 +5915,30 @@
       <c r="C18" s="13"/>
       <c r="G18" s="27"/>
       <c r="J18" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
       <c r="N18" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
       <c r="R18" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S18" s="23"/>
       <c r="T18" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U18" s="35"/>
       <c r="V18" s="35"/>
       <c r="W18" s="35"/>
       <c r="X18" s="39"/>
       <c r="Y18" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z18" s="35"/>
       <c r="AA18" s="35"/>
@@ -5973,30 +5955,30 @@
       <c r="C19" s="13"/>
       <c r="G19" s="27"/>
       <c r="J19" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
       <c r="N19" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
       <c r="R19" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S19" s="23"/>
       <c r="T19" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U19" s="35"/>
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
       <c r="X19" s="39"/>
       <c r="Y19" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z19" s="35"/>
       <c r="AA19" s="35"/>
@@ -6013,30 +5995,30 @@
       <c r="C20" s="13"/>
       <c r="G20" s="27"/>
       <c r="J20" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
       <c r="N20" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
       <c r="R20" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S20" s="23"/>
       <c r="T20" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U20" s="35"/>
       <c r="V20" s="35"/>
       <c r="W20" s="35"/>
       <c r="X20" s="39"/>
       <c r="Y20" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z20" s="35"/>
       <c r="AA20" s="35"/>
@@ -6053,30 +6035,30 @@
       <c r="C21" s="13"/>
       <c r="G21" s="27"/>
       <c r="J21" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
       <c r="N21" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O21" s="23"/>
       <c r="P21" s="23"/>
       <c r="Q21" s="23"/>
       <c r="R21" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S21" s="23"/>
       <c r="T21" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U21" s="35"/>
       <c r="V21" s="35"/>
       <c r="W21" s="35"/>
       <c r="X21" s="39"/>
       <c r="Y21" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z21" s="35"/>
       <c r="AA21" s="35"/>
@@ -6093,30 +6075,30 @@
       <c r="C22" s="13"/>
       <c r="G22" s="27"/>
       <c r="J22" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
       <c r="N22" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O22" s="23"/>
       <c r="P22" s="23"/>
       <c r="Q22" s="23"/>
       <c r="R22" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S22" s="23"/>
       <c r="T22" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U22" s="35"/>
       <c r="V22" s="35"/>
       <c r="W22" s="35"/>
       <c r="X22" s="39"/>
       <c r="Y22" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z22" s="35"/>
       <c r="AA22" s="35"/>
@@ -6133,30 +6115,30 @@
       <c r="C23" s="13"/>
       <c r="G23" s="27"/>
       <c r="J23" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
       <c r="N23" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O23" s="23"/>
       <c r="P23" s="23"/>
       <c r="Q23" s="23"/>
       <c r="R23" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U23" s="35"/>
       <c r="V23" s="35"/>
       <c r="W23" s="35"/>
       <c r="X23" s="39"/>
       <c r="Y23" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z23" s="35"/>
       <c r="AA23" s="35"/>
@@ -6173,30 +6155,30 @@
       <c r="C24" s="13"/>
       <c r="G24" s="27"/>
       <c r="J24" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
       <c r="M24" s="23"/>
       <c r="N24" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U24" s="35"/>
       <c r="V24" s="35"/>
       <c r="W24" s="35"/>
       <c r="X24" s="39"/>
       <c r="Y24" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z24" s="35"/>
       <c r="AA24" s="35"/>
@@ -6213,30 +6195,30 @@
       <c r="C25" s="13"/>
       <c r="G25" s="27"/>
       <c r="J25" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
       <c r="M25" s="23"/>
       <c r="N25" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O25" s="23"/>
       <c r="P25" s="23"/>
       <c r="Q25" s="23"/>
       <c r="R25" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S25" s="23"/>
       <c r="T25" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U25" s="35"/>
       <c r="V25" s="35"/>
       <c r="W25" s="35"/>
       <c r="X25" s="39"/>
       <c r="Y25" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z25" s="35"/>
       <c r="AA25" s="35"/>
@@ -6253,30 +6235,30 @@
       <c r="C26" s="13"/>
       <c r="G26" s="27"/>
       <c r="J26" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
       <c r="M26" s="23"/>
       <c r="N26" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S26" s="23"/>
       <c r="T26" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U26" s="35"/>
       <c r="V26" s="35"/>
       <c r="W26" s="35"/>
       <c r="X26" s="39"/>
       <c r="Y26" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z26" s="35"/>
       <c r="AA26" s="35"/>
@@ -6293,30 +6275,30 @@
       <c r="C27" s="13"/>
       <c r="G27" s="27"/>
       <c r="J27" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O27" s="23"/>
       <c r="P27" s="23"/>
       <c r="Q27" s="23"/>
       <c r="R27" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S27" s="23"/>
       <c r="T27" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U27" s="35"/>
       <c r="V27" s="35"/>
       <c r="W27" s="35"/>
       <c r="X27" s="39"/>
       <c r="Y27" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z27" s="35"/>
       <c r="AA27" s="35"/>
@@ -6333,30 +6315,30 @@
       <c r="C28" s="13"/>
       <c r="G28" s="27"/>
       <c r="J28" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
       <c r="N28" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O28" s="23"/>
       <c r="P28" s="23"/>
       <c r="Q28" s="23"/>
       <c r="R28" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S28" s="23"/>
       <c r="T28" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U28" s="35"/>
       <c r="V28" s="35"/>
       <c r="W28" s="35"/>
       <c r="X28" s="39"/>
       <c r="Y28" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z28" s="35"/>
       <c r="AA28" s="35"/>
@@ -6373,30 +6355,30 @@
       <c r="C29" s="13"/>
       <c r="G29" s="27"/>
       <c r="J29" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
       <c r="N29" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O29" s="23"/>
       <c r="P29" s="23"/>
       <c r="Q29" s="23"/>
       <c r="R29" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S29" s="23"/>
       <c r="T29" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U29" s="35"/>
       <c r="V29" s="35"/>
       <c r="W29" s="35"/>
       <c r="X29" s="39"/>
       <c r="Y29" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z29" s="35"/>
       <c r="AA29" s="35"/>
@@ -6413,30 +6395,30 @@
       <c r="C30" s="13"/>
       <c r="G30" s="27"/>
       <c r="J30" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
       <c r="M30" s="23"/>
       <c r="N30" s="23" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O30" s="23"/>
       <c r="P30" s="23"/>
       <c r="Q30" s="23"/>
       <c r="R30" s="23" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="S30" s="23"/>
       <c r="T30" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="U30" s="35"/>
       <c r="V30" s="35"/>
       <c r="W30" s="35"/>
       <c r="X30" s="39"/>
       <c r="Y30" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z30" s="35"/>
       <c r="AA30" s="35"/>
@@ -6670,7 +6652,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -6708,7 +6690,7 @@
       <c r="AC1" s="23"/>
       <c r="AD1" s="23"/>
       <c r="AE1" s="23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AF1" s="23"/>
       <c r="AG1" s="23"/>
@@ -6718,8 +6700,8 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="159" t="s">
-        <v>109</v>
+      <c r="AL1" s="150" t="s">
+        <v>114</v>
       </c>
       <c r="AM1" s="23"/>
       <c r="AN1" s="23"/>
@@ -6846,7 +6828,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
@@ -6877,7 +6859,7 @@
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="55" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="56"/>
@@ -6981,7 +6963,7 @@
       </c>
       <c r="B7" s="87"/>
       <c r="C7" s="88" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D7" s="88"/>
       <c r="E7" s="88"/>
@@ -7131,7 +7113,7 @@
       </c>
       <c r="B10" s="87"/>
       <c r="C10" s="88" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D10" s="88"/>
       <c r="E10" s="88"/>
@@ -7181,7 +7163,7 @@
       </c>
       <c r="B11" s="87"/>
       <c r="C11" s="88" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D11" s="88"/>
       <c r="E11" s="88"/>
@@ -7190,7 +7172,7 @@
       <c r="H11" s="88"/>
       <c r="I11" s="88"/>
       <c r="J11" s="19" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
@@ -7231,7 +7213,7 @@
       </c>
       <c r="B12" s="87"/>
       <c r="C12" s="88" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="88"/>
@@ -7281,7 +7263,7 @@
       </c>
       <c r="B13" s="87"/>
       <c r="C13" s="88" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D13" s="88"/>
       <c r="E13" s="88"/>
@@ -7290,7 +7272,7 @@
       <c r="H13" s="88"/>
       <c r="I13" s="88"/>
       <c r="J13" s="19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
@@ -7340,7 +7322,7 @@
       <c r="H14" s="88"/>
       <c r="I14" s="88"/>
       <c r="J14" s="19" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -7381,7 +7363,7 @@
       </c>
       <c r="B15" s="87"/>
       <c r="C15" s="88" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D15" s="88"/>
       <c r="E15" s="88"/>
@@ -7390,7 +7372,7 @@
       <c r="H15" s="88"/>
       <c r="I15" s="88"/>
       <c r="J15" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="19"/>
@@ -7431,7 +7413,7 @@
       </c>
       <c r="B16" s="87"/>
       <c r="C16" s="88" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D16" s="88"/>
       <c r="E16" s="88"/>
@@ -7481,7 +7463,7 @@
       </c>
       <c r="B17" s="87"/>
       <c r="C17" s="88" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D17" s="88"/>
       <c r="E17" s="88"/>
@@ -7531,7 +7513,7 @@
       </c>
       <c r="B18" s="87"/>
       <c r="C18" s="88" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D18" s="88"/>
       <c r="E18" s="88"/>
@@ -7581,7 +7563,7 @@
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="88" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D19" s="88"/>
       <c r="E19" s="88"/>
@@ -8712,7 +8694,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:37">
       <c r="A1" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8903,7 +8885,7 @@
       <c r="B5" s="54"/>
       <c r="C5" s="54"/>
       <c r="D5" s="55" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="56"/>
@@ -8945,7 +8927,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:37">
       <c r="A6" s="57" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B6" s="57"/>
       <c r="C6" s="57"/>
@@ -8954,7 +8936,7 @@
       <c r="F6" s="57"/>
       <c r="G6" s="57"/>
       <c r="H6" s="58" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I6" s="69"/>
       <c r="J6" s="69"/>
@@ -8980,7 +8962,7 @@
       <c r="AD6" s="69"/>
       <c r="AE6" s="78"/>
       <c r="AF6" s="57" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AG6" s="57"/>
       <c r="AH6" s="57"/>
@@ -10362,7 +10344,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10400,7 +10382,7 @@
       <c r="AC1" s="23"/>
       <c r="AD1" s="23"/>
       <c r="AE1" s="23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AF1" s="23"/>
       <c r="AG1" s="23"/>
@@ -10410,8 +10392,8 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="159" t="s">
-        <v>109</v>
+      <c r="AL1" s="150" t="s">
+        <v>114</v>
       </c>
       <c r="AM1" s="23"/>
       <c r="AN1" s="23"/>
@@ -10538,7 +10520,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
@@ -10569,7 +10551,7 @@
       <c r="B5" s="40"/>
       <c r="C5" s="40"/>
       <c r="D5" s="41" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E5" s="42"/>
       <c r="F5" s="43"/>
@@ -10615,11 +10597,11 @@
     </row>
     <row r="6" customHeight="1" spans="1:41">
       <c r="A6" s="25" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="44" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="44"/>
@@ -10677,7 +10659,7 @@
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="J7" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -10716,7 +10698,7 @@
       </c>
       <c r="B8" s="46"/>
       <c r="C8" s="47" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="47"/>
@@ -10852,7 +10834,7 @@
       </c>
       <c r="B11" s="33"/>
       <c r="C11" s="49" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="49"/>
@@ -10898,7 +10880,7 @@
       </c>
       <c r="B12" s="33"/>
       <c r="C12" s="49" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="49"/>
@@ -10944,7 +10926,7 @@
       </c>
       <c r="B13" s="46"/>
       <c r="C13" s="47" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -11036,7 +11018,7 @@
       </c>
       <c r="B15" s="46"/>
       <c r="C15" s="47" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D15" s="47"/>
       <c r="E15" s="47"/>
@@ -11082,7 +11064,7 @@
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="47" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -11128,7 +11110,7 @@
       </c>
       <c r="B17" s="46"/>
       <c r="C17" s="47" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D17" s="47"/>
       <c r="E17" s="47"/>
@@ -11174,7 +11156,7 @@
       </c>
       <c r="B18" s="46"/>
       <c r="C18" s="47" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
@@ -11220,7 +11202,7 @@
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="47" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
@@ -11524,7 +11506,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -11562,7 +11544,7 @@
       <c r="AC1" s="23"/>
       <c r="AD1" s="23"/>
       <c r="AE1" s="23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AF1" s="23"/>
       <c r="AG1" s="23"/>
@@ -11572,8 +11554,8 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="159" t="s">
-        <v>109</v>
+      <c r="AL1" s="150" t="s">
+        <v>114</v>
       </c>
       <c r="AM1" s="23"/>
       <c r="AN1" s="23"/>
@@ -11700,7 +11682,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
@@ -11726,7 +11708,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:41">
       <c r="A5" s="25" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -11737,7 +11719,7 @@
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="J5" s="25" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
@@ -11757,7 +11739,7 @@
       <c r="Z5" s="35"/>
       <c r="AA5" s="35"/>
       <c r="AB5" s="25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC5" s="25"/>
       <c r="AD5" s="25"/>
@@ -11788,7 +11770,7 @@
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="J6" s="36" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K6" s="37"/>
       <c r="L6" s="37"/>
@@ -12053,7 +12035,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:41">
       <c r="A1" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -12091,7 +12073,7 @@
       <c r="AC1" s="23"/>
       <c r="AD1" s="23"/>
       <c r="AE1" s="23" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AF1" s="23"/>
       <c r="AG1" s="23"/>
@@ -12101,8 +12083,8 @@
       </c>
       <c r="AJ1" s="23"/>
       <c r="AK1" s="23"/>
-      <c r="AL1" s="159" t="s">
-        <v>109</v>
+      <c r="AL1" s="150" t="s">
+        <v>114</v>
       </c>
       <c r="AM1" s="23"/>
       <c r="AN1" s="23"/>
@@ -12229,7 +12211,7 @@
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
       <c r="T4" s="23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="U4" s="23"/>
       <c r="V4" s="23"/>
@@ -12298,7 +12280,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:41">
       <c r="A6" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
